--- a/src/nodes/P/compressor_blade_parameters.xlsx
+++ b/src/nodes/P/compressor_blade_parameters.xlsx
@@ -803,16 +803,16 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>37</v>
       </c>
       <c r="D3">
-        <v>119.99882824293194</v>
+        <v>119.86707516339082</v>
       </c>
       <c r="E3">
-        <v>119.30116918046657</v>
+        <v>119.27834883006949</v>
       </c>
       <c r="F3">
         <v>161.2955125594973</v>
@@ -821,103 +821,103 @@
         <v>143.9868199114384</v>
       </c>
       <c r="H3">
-        <v>311.48991489418455</v>
+        <v>298.3782062802938</v>
       </c>
       <c r="I3">
         <v>2310.3654248608714</v>
       </c>
       <c r="J3">
-        <v>960.29156912133215</v>
+        <v>943.3177706848345</v>
       </c>
       <c r="K3">
         <v>39814.695671117195</v>
       </c>
       <c r="L3">
-        <v>16761.583174932406</v>
+        <v>17775.753534837091</v>
       </c>
       <c r="M3">
         <v>146612.39974726515</v>
       </c>
       <c r="N3">
-        <v>53.810997960002794</v>
+        <v>59.574570664650714</v>
       </c>
       <c r="O3">
         <v>63.458532650130032</v>
       </c>
       <c r="P3">
-        <v>3.0828977864260882</v>
+        <v>3.1614834824722093</v>
       </c>
       <c r="Q3">
         <v>17.23307284756255</v>
       </c>
       <c r="R3">
-        <v>3496.8916951060842</v>
+        <v>3460.8348579226836</v>
       </c>
       <c r="S3">
         <v>819751.96376448066</v>
       </c>
       <c r="T3">
-        <v>1153934.5207253741</v>
+        <v>1289727.280846379</v>
       </c>
       <c r="U3">
         <v>11903414.499537855</v>
       </c>
       <c r="V3">
-        <v>53732.667629772572</v>
+        <v>56197.589947496708</v>
       </c>
       <c r="W3">
         <v>2623406.5767247276</v>
       </c>
       <c r="X3">
-        <v>536.41094233829449</v>
+        <v>478.55130718007212</v>
       </c>
       <c r="Y3">
         <v>133622.41286058465</v>
       </c>
       <c r="Z3">
-        <v>251977.0026926696</v>
+        <v>230744.39576781186</v>
       </c>
       <c r="AA3">
         <v>2599606.7432621135</v>
       </c>
       <c r="AB3">
-        <v>2058.4199627766898</v>
+        <v>-0.16124138774757577</v>
       </c>
       <c r="AC3">
         <v>96824.41152414633</v>
       </c>
       <c r="AD3">
-        <v>0.46901034702844457</v>
+        <v>-4.0120804813246885E-05</v>
       </c>
       <c r="AE3">
         <v>2.2450542964408755</v>
       </c>
       <c r="AF3">
-        <v>519.56080375687441</v>
+        <v>478.55130706716443</v>
       </c>
       <c r="AG3">
         <v>129826.54201254154</v>
       </c>
       <c r="AH3">
-        <v>251993.85283125105</v>
+        <v>230744.39576792475</v>
       </c>
       <c r="AI3">
         <v>2603402.6141101564</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-2.0838624216365386E-17</v>
       </c>
       <c r="AK3">
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>252513.41363500792</v>
+        <v>231222.94707499194</v>
       </c>
       <c r="AM3">
         <v>2733229.156122698</v>
       </c>
       <c r="AN3">
-        <v>3860.4420014278494</v>
+        <v>3875.7820351241721</v>
       </c>
       <c r="AO3">
         <v>34617.317468734174</v>
@@ -1404,124 +1404,124 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>37</v>
       </c>
       <c r="D3">
-        <v>134.47644419818192</v>
+        <v>134.75128662534979</v>
       </c>
       <c r="E3">
-        <v>133.45796404107321</v>
+        <v>133.53894639881798</v>
       </c>
       <c r="F3">
-        <v>166.88265294488286</v>
+        <v>166.60044829595643</v>
       </c>
       <c r="G3">
-        <v>165.53700641365069</v>
+        <v>165.55607037679593</v>
       </c>
       <c r="H3">
-        <v>649.75418237927045</v>
+        <v>779.70501885512442</v>
       </c>
       <c r="I3">
-        <v>1151.8711609832421</v>
+        <v>892.70014976201276</v>
       </c>
       <c r="J3">
-        <v>1767.2775950710029</v>
+        <v>2120.7331140852029</v>
       </c>
       <c r="K3">
-        <v>4165.0358110546658</v>
+        <v>3227.9027535673672</v>
       </c>
       <c r="L3">
-        <v>39115.44740191981</v>
+        <v>46938.536882303772</v>
       </c>
       <c r="M3">
-        <v>95338.481765029239</v>
+        <v>73887.323367897669</v>
       </c>
       <c r="N3">
-        <v>60.200378024019521</v>
+        <v>60.200378024019528</v>
       </c>
       <c r="O3">
         <v>82.768355519594664</v>
       </c>
       <c r="P3">
-        <v>2.7199172286965267</v>
+        <v>2.7199172286965263</v>
       </c>
       <c r="Q3">
-        <v>3.6158868735800045</v>
+        <v>3.6158868735800058</v>
       </c>
       <c r="R3">
-        <v>7040.471630945417</v>
+        <v>9375.1225895835</v>
       </c>
       <c r="S3">
-        <v>22925.841753428842</v>
+        <v>15737.607836034256</v>
       </c>
       <c r="T3">
-        <v>3012607.8495603153</v>
+        <v>3615129.4194723777</v>
       </c>
       <c r="U3">
-        <v>9610400.8666512314</v>
+        <v>7448060.6716547059</v>
       </c>
       <c r="V3">
-        <v>110631.71475283604</v>
+        <v>132758.05770340317</v>
       </c>
       <c r="W3">
-        <v>344732.17566018039</v>
+        <v>267167.43613663985</v>
       </c>
       <c r="X3">
-        <v>2233.6228522224319</v>
+        <v>3606.9040551159214</v>
       </c>
       <c r="Y3">
-        <v>7865.543436245629</v>
+        <v>4065.87664021726</v>
       </c>
       <c r="Z3">
-        <v>657843.12938609067</v>
+        <v>789411.755263308</v>
       </c>
       <c r="AA3">
-        <v>1719391.5132248981</v>
+        <v>1332528.4227492972</v>
       </c>
       <c r="AB3">
-        <v>4240.935456181578</v>
+        <v>5089.1225474178154</v>
       </c>
       <c r="AC3">
-        <v>-0.98910103546999006</v>
+        <v>-0.76655330249534814</v>
       </c>
       <c r="AD3">
-        <v>0.37060802963876138</v>
+        <v>0.37104497139144288</v>
       </c>
       <c r="AE3">
-        <v>-3.3111571687938093E-05</v>
+        <v>-3.3060976490015982E-05</v>
       </c>
       <c r="AF3">
-        <v>2206.1906981106</v>
+        <v>3573.9466585398786</v>
       </c>
       <c r="AG3">
-        <v>7865.5434356740225</v>
+        <v>4065.8766397749409</v>
       </c>
       <c r="AH3">
-        <v>657870.56154020235</v>
+        <v>789444.71265988413</v>
       </c>
       <c r="AI3">
-        <v>1719391.5132254697</v>
+        <v>1332528.4227497396</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-1.0696252980538481E-12</v>
       </c>
       <c r="AK3">
         <v>-1.5527897657352211E-16</v>
       </c>
       <c r="AL3">
-        <v>660076.75223831309</v>
+        <v>793018.65931842383</v>
       </c>
       <c r="AM3">
-        <v>1727257.0566611437</v>
+        <v>1336594.2993895146</v>
       </c>
       <c r="AN3">
-        <v>9024.0458406210855</v>
+        <v>10841.522156159283</v>
       </c>
       <c r="AO3">
-        <v>20848.682238261583</v>
+        <v>16133.226795616853</v>
       </c>
       <c r="AP3">
         <v>46.65367795387116</v>
@@ -2005,106 +2005,106 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>37</v>
       </c>
       <c r="D3">
-        <v>144.74254028800721</v>
+        <v>145.44974581118692</v>
       </c>
       <c r="E3">
-        <v>143.38267869751354</v>
+        <v>143.73465253234517</v>
       </c>
       <c r="F3">
-        <v>182.81487348587726</v>
+        <v>182.74644743359829</v>
       </c>
       <c r="G3">
-        <v>182.71117720448109</v>
+        <v>182.67728116866502</v>
       </c>
       <c r="H3">
-        <v>1046.60611404446</v>
+        <v>1345.6364323428768</v>
       </c>
       <c r="I3">
-        <v>701.28049855759764</v>
+        <v>467.52167377493544</v>
       </c>
       <c r="J3">
-        <v>2759.8826083020026</v>
+        <v>3548.420496388288</v>
       </c>
       <c r="K3">
-        <v>388.39706809008345</v>
+        <v>258.93137872672236</v>
       </c>
       <c r="L3">
-        <v>67582.703361327454</v>
+        <v>86892.047178849549</v>
       </c>
       <c r="M3">
-        <v>64049.3925005803</v>
+        <v>42699.595000386878</v>
       </c>
       <c r="N3">
         <v>64.573197552003322</v>
       </c>
       <c r="O3">
-        <v>91.332059899452346</v>
+        <v>91.331797851456244</v>
       </c>
       <c r="P3">
-        <v>2.6369830744030627</v>
+        <v>2.6369830744030622</v>
       </c>
       <c r="Q3">
-        <v>0.55383982427708078</v>
+        <v>0.55383823521168285</v>
       </c>
       <c r="R3">
-        <v>14379.18092576731</v>
+        <v>23840.673919852146</v>
       </c>
       <c r="S3">
-        <v>1449.2936940813954</v>
+        <v>516.02408896650206</v>
       </c>
       <c r="T3">
-        <v>5583399.2147067459</v>
+        <v>7178656.1331943879</v>
       </c>
       <c r="U3">
-        <v>7124382.24685532</v>
+        <v>4749588.1645702133</v>
       </c>
       <c r="V3">
-        <v>185319.87334260825</v>
+        <v>238268.40858335339</v>
       </c>
       <c r="W3">
-        <v>35473.0025089018</v>
+        <v>23648.668339267875</v>
       </c>
       <c r="X3">
-        <v>7101.4172003355516</v>
+        <v>14483.549130011321</v>
       </c>
       <c r="Y3">
-        <v>1234.18393014065</v>
+        <v>372.61799113156627</v>
       </c>
       <c r="Z3">
-        <v>1219367.9594573109</v>
+        <v>1567758.8050165433</v>
       </c>
       <c r="AA3">
-        <v>1274619.2944687847</v>
+        <v>849757.3856558284</v>
       </c>
       <c r="AB3">
-        <v>7105.428456384836</v>
+        <v>9135.5508724948413</v>
       </c>
       <c r="AC3">
-        <v>-0.10177867337629369</v>
+        <v>1.1315911942103971E-11</v>
       </c>
       <c r="AD3">
-        <v>0.33581097998823356</v>
+        <v>0.33696820109109316</v>
       </c>
       <c r="AE3">
-        <v>-4.5795167389976518E-06</v>
+        <v>7.6332190110594088E-16</v>
       </c>
       <c r="AF3">
-        <v>7059.7717556697708</v>
+        <v>14429.820466879384</v>
       </c>
       <c r="AG3">
-        <v>1234.1839301325151</v>
+        <v>372.61799113156627</v>
       </c>
       <c r="AH3">
-        <v>1219409.6049019767</v>
+        <v>1567812.5336796751</v>
       </c>
       <c r="AI3">
-        <v>1274619.2944687926</v>
+        <v>849757.3856558284</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -2113,16 +2113,16 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>1226469.3766576462</v>
+        <v>1582242.3541465544</v>
       </c>
       <c r="AM3">
-        <v>1275853.4783989254</v>
+        <v>850130.00364696</v>
       </c>
       <c r="AN3">
-        <v>15633.832573848667</v>
+        <v>20168.878674648146</v>
       </c>
       <c r="AO3">
-        <v>13969.136602849687</v>
+        <v>9307.97809109926</v>
       </c>
       <c r="AP3">
         <v>50.042495777034276</v>
